--- a/eoptolink/dist/20261026_新易盛模型_v0.2.2.xlsx
+++ b/eoptolink/dist/20261026_新易盛模型_v0.2.2.xlsx
@@ -6717,26 +6717,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6954,26 +6954,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7075,26 +7075,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7196,26 +7196,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7317,26 +7317,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -7438,26 +7438,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tsmc/dist/20261025_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台積電模型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">_v0.3.1.xlsx</t>
+      <t xml:space="preserve">tsmc/dist/20261028_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台積電個股模型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">_v0.4.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -36393,7 +36393,7 @@
         <v>32</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>781.872916666667</v>
+        <v>781.872916666666</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>33</v>
@@ -39779,7 +39779,7 @@
       </c>
       <c r="C11" s="20" t="n">
         <f aca="false">PL!D71/itc_26</f>
-        <v>0.00925820928732542</v>
+        <v>0.00925820928732543</v>
       </c>
       <c r="D11" s="20" t="n">
         <f aca="false">PL!E71/itc_27</f>
